--- a/backend/src/test/resources/amostras/balancete.xlsx
+++ b/backend/src/test/resources/amostras/balancete.xlsx
@@ -40,7 +40,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Período: 01/01/2024 a 31/12/2024</t>
+          <t>Período: 01/01/2021 a 31/12/2021</t>
         </is>
       </c>
     </row>
